--- a/nr-update-patient-relationship-discr/ig/ValueSet-fr-core-vs-schedule-type.xlsx
+++ b/nr-update-patient-relationship-discr/ig/ValueSet-fr-core-vs-schedule-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:02:57+00:00</t>
+    <t>2026-03-20T07:20:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
